--- a/data/trans_orig/P64B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2007</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2007 (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>42128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61868</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94781</t>
+          <t>94562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81332</t>
+          <t>81573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118165</t>
+          <t>119296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82570</t>
+          <t>82328</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116337</t>
+          <t>118402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45514</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69563</t>
+          <t>69841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>136322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178269</t>
+          <t>178279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142235</t>
+          <t>141672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181247</t>
+          <t>181519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47233</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70923</t>
+          <t>70695</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>198259</t>
+          <t>198263</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242502</t>
+          <t>243359</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>50059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66804</t>
+          <t>64490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>68488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105365</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111242</t>
+          <t>113097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>157604</t>
+          <t>158096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126397</t>
+          <t>123925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168864</t>
+          <t>167723</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72553</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>104463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>205172</t>
+          <t>204785</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257685</t>
+          <t>258545</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239209</t>
+          <t>239338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287912</t>
+          <t>286812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79369</t>
+          <t>78367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>110272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>328553</t>
+          <t>327215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385954</t>
+          <t>387783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>49239</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60597</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93309</t>
+          <t>93590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66306</t>
+          <t>65862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109793</t>
+          <t>109445</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152231</t>
+          <t>150240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35332</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75282</t>
+          <t>76090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>113569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52725</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78008</t>
+          <t>78324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133565</t>
+          <t>137159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179886</t>
+          <t>180831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165579</t>
+          <t>164258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206634</t>
+          <t>205988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47282</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>219675</t>
+          <t>220510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270299</t>
+          <t>270256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51834</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>80155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114814</t>
+          <t>116424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>57361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88945</t>
+          <t>89277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146973</t>
+          <t>149550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>192351</t>
+          <t>196238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155953</t>
+          <t>154417</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>197547</t>
+          <t>197829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127086</t>
+          <t>126153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167017</t>
+          <t>164743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294375</t>
+          <t>293223</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>350408</t>
+          <t>351476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>203298</t>
+          <t>205491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250532</t>
+          <t>250161</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>100487</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>138996</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>318539</t>
+          <t>319276</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>378652</t>
+          <t>376678</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>94877</t>
+          <t>95834</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>142445</t>
+          <t>143924</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>195649</t>
+          <t>195175</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>306943</t>
+          <t>302648</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>373350</t>
+          <t>372848</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>169200</t>
+          <t>172749</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>220875</t>
+          <t>220258</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>487927</t>
+          <t>489913</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>576142</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>51988</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>65108</t>
+          <t>68011</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44267</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>74544</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>77814</t>
+          <t>78032</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>114667</t>
+          <t>115829</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>473466</t>
+          <t>471677</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>549898</t>
+          <t>551550</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>327702</t>
+          <t>327297</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>387033</t>
+          <t>392476</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>816613</t>
+          <t>817992</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>914880</t>
+          <t>922726</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>796302</t>
+          <t>789797</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>879524</t>
+          <t>879145</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>305948</t>
+          <t>302321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>365369</t>
+          <t>364824</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1118623</t>
+          <t>1118914</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1225943</t>
+          <t>1223211</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2012</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2012 (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39134</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>47631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74485</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>72719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108931</t>
+          <t>107266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53561</t>
+          <t>54403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83155</t>
+          <t>82417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65470</t>
+          <t>65733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>103176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141482</t>
+          <t>141210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92510</t>
+          <t>90524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125059</t>
+          <t>125777</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>46012</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70928</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148611</t>
+          <t>146886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190459</t>
+          <t>188635</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32549</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68668</t>
+          <t>68460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103736</t>
+          <t>103075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>47996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102370</t>
+          <t>102362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>143700</t>
+          <t>142588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25464</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>29298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>42885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>96082</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>134325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79211</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110300</t>
+          <t>112567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>184951</t>
+          <t>185852</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>236637</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143431</t>
+          <t>142293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185065</t>
+          <t>184601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74252</t>
+          <t>75274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107416</t>
+          <t>106410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228743</t>
+          <t>228184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283284</t>
+          <t>281085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84875</t>
+          <t>82864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41645</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77387</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116188</t>
+          <t>116917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16697</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>65992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99009</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>61630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90421</t>
+          <t>91224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>139273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181797</t>
+          <t>183745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110364</t>
+          <t>108415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147242</t>
+          <t>146372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60689</t>
+          <t>59471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88672</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>177274</t>
+          <t>179089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>226696</t>
+          <t>226215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34144</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56254</t>
+          <t>55418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>100900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141310</t>
+          <t>137855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71742</t>
+          <t>69891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>151744</t>
+          <t>152985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>200531</t>
+          <t>199852</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39557</t>
+          <t>39913</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92036</t>
+          <t>90004</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127339</t>
+          <t>128013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106991</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140577</t>
+          <t>142097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207445</t>
+          <t>207990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257418</t>
+          <t>257972</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>115638</t>
+          <t>113956</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>155149</t>
+          <t>154021</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58220</t>
+          <t>58700</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89079</t>
+          <t>88360</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180815</t>
+          <t>182136</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>229888</t>
+          <t>230231</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>58515</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>97098</t>
+          <t>97974</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51286</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>83976</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>120963</t>
+          <t>119438</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>169700</t>
+          <t>169762</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>301410</t>
+          <t>299810</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>367810</t>
+          <t>366852</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>127384</t>
+          <t>127982</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>176730</t>
+          <t>173888</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>441112</t>
+          <t>441480</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>525430</t>
+          <t>525221</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32005</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>59995</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41882</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74359</t>
+          <t>73356</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41264</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>53824</t>
+          <t>53501</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>87849</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>76485</t>
+          <t>76384</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>116877</t>
+          <t>117703</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>336885</t>
+          <t>342095</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>408611</t>
+          <t>405357</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>318990</t>
+          <t>315662</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>380330</t>
+          <t>377319</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>675113</t>
+          <t>678490</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>766786</t>
+          <t>768631</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>496083</t>
+          <t>494579</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>569538</t>
+          <t>571213</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>264501</t>
+          <t>270507</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>323244</t>
+          <t>329850</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>782461</t>
+          <t>780944</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>876998</t>
+          <t>877448</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2016</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2016 (tasa de respuesta: 94,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26530</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35036</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>59670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>47361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74380</t>
+          <t>74771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>34858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>57263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87952</t>
+          <t>88395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123728</t>
+          <t>122406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98655</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129472</t>
+          <t>129040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79225</t>
+          <t>79921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>162247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>201581</t>
+          <t>200907</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29578</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>55071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24900</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>47456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61704</t>
+          <t>60422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95269</t>
+          <t>94911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54764</t>
+          <t>53519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84729</t>
+          <t>86652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124922</t>
+          <t>124030</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39823</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100395</t>
+          <t>103271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>139893</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67796</t>
+          <t>68237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97743</t>
+          <t>97178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>180325</t>
+          <t>181429</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>230413</t>
+          <t>230462</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125375</t>
+          <t>125038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166580</t>
+          <t>165558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62281</t>
+          <t>62084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91732</t>
+          <t>90560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199971</t>
+          <t>198459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250569</t>
+          <t>246119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>60930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70063</t>
+          <t>71074</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103459</t>
+          <t>105803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51314</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78334</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127644</t>
+          <t>128005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172185</t>
+          <t>173349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54186</t>
+          <t>54475</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63011</t>
+          <t>64534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96795</t>
+          <t>97379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80734</t>
+          <t>81383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127319</t>
+          <t>126838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171052</t>
+          <t>168566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109207</t>
+          <t>108303</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146981</t>
+          <t>146034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66052</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>95221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183500</t>
+          <t>182725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232351</t>
+          <t>230420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48042</t>
+          <t>47609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>84372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>58270</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94172</t>
+          <t>93797</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>132137</t>
+          <t>136817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104619</t>
+          <t>103109</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140293</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122162</t>
+          <t>120802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157223</t>
+          <t>156503</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235791</t>
+          <t>234116</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>284397</t>
+          <t>286706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>112289</t>
+          <t>109656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147778</t>
+          <t>147565</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58096</t>
+          <t>57380</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87591</t>
+          <t>86703</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>177172</t>
+          <t>177130</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>224892</t>
+          <t>223950</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>123475</t>
+          <t>125564</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171666</t>
+          <t>172246</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101433</t>
+          <t>100767</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>141553</t>
+          <t>143257</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>236686</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>299413</t>
+          <t>299563</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>222812</t>
+          <t>222196</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>282591</t>
+          <t>283537</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>141569</t>
+          <t>138871</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185995</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>376661</t>
+          <t>379470</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>453543</t>
+          <t>453865</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36744</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45319</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42746</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>56289</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>92825</t>
+          <t>91810</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>85528</t>
+          <t>84491</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>124171</t>
+          <t>125812</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>349034</t>
+          <t>345134</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>413613</t>
+          <t>411814</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>301784</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>363972</t>
+          <t>362837</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,47 +12828,47 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>36,66%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>714041</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>672496</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>763169</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
           <t>30,49%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>714041</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>667520</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>757902</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>30,49%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>476343</t>
+          <t>478631</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>550033</t>
+          <t>553039</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>267383</t>
+          <t>267843</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>325617</t>
+          <t>324600</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>759488</t>
+          <t>763154</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>858986</t>
+          <t>853926</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94562</t>
+          <t>94553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119296</t>
+          <t>119439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82328</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118402</t>
+          <t>118005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45597</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69841</t>
+          <t>70367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136322</t>
+          <t>136288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178279</t>
+          <t>179657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141672</t>
+          <t>142621</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181519</t>
+          <t>180169</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70695</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>198263</t>
+          <t>197541</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>243359</t>
+          <t>245128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24477</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68488</t>
+          <t>69012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>104311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35417</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61899</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113097</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>157270</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39458</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123925</t>
+          <t>123856</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167723</t>
+          <t>168087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71279</t>
+          <t>73365</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104463</t>
+          <t>103485</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>204785</t>
+          <t>207550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>258545</t>
+          <t>259151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239338</t>
+          <t>241862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286812</t>
+          <t>288303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78367</t>
+          <t>79053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>111251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>327215</t>
+          <t>327909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387783</t>
+          <t>384999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>61146</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>92735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65862</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109445</t>
+          <t>108805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150240</t>
+          <t>151438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76090</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113569</t>
+          <t>110726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78324</t>
+          <t>77959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137159</t>
+          <t>136694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180831</t>
+          <t>180777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164258</t>
+          <t>162522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205988</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47976</t>
+          <t>48537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220510</t>
+          <t>221937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270256</t>
+          <t>271629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52703</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80155</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116424</t>
+          <t>115853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57361</t>
+          <t>56601</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89277</t>
+          <t>88058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149550</t>
+          <t>147822</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>196238</t>
+          <t>195317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48966</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>154417</t>
+          <t>153437</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>197829</t>
+          <t>194677</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126153</t>
+          <t>128080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>164743</t>
+          <t>165990</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>293223</t>
+          <t>292088</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>351476</t>
+          <t>352364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>205491</t>
+          <t>205026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250161</t>
+          <t>251720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>103875</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>138886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319276</t>
+          <t>319838</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>376678</t>
+          <t>380600</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>95834</t>
+          <t>94229</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>138898</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>143924</t>
+          <t>141451</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>195175</t>
+          <t>194412</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>302648</t>
+          <t>303251</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>367260</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>172749</t>
+          <t>172207</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>220258</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>489913</t>
+          <t>487395</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>576143</t>
+          <t>572085</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>51991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>118041</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>471677</t>
+          <t>472391</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>551550</t>
+          <t>552222</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>327297</t>
+          <t>325894</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>386996</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>817992</t>
+          <t>818615</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>922726</t>
+          <t>925255</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>789797</t>
+          <t>791207</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>879145</t>
+          <t>879699</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>302321</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>363157</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1118914</t>
+          <t>1117450</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1223211</t>
+          <t>1224374</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4989,47 +4989,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>26477</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>37792</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>26477</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>18121</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38865</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>75239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72719</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107266</t>
+          <t>107771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82417</t>
+          <t>81797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>40801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65733</t>
+          <t>66235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103176</t>
+          <t>103297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>139847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>93276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125777</t>
+          <t>124149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46012</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146886</t>
+          <t>147391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>188635</t>
+          <t>187896</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34059</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68460</t>
+          <t>68108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103075</t>
+          <t>102841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>49244</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102362</t>
+          <t>102591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142588</t>
+          <t>145923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42885</t>
+          <t>45500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96082</t>
+          <t>97799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>134325</t>
+          <t>136228</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>78216</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112567</t>
+          <t>111377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185852</t>
+          <t>183489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233839</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>142293</t>
+          <t>140378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184601</t>
+          <t>181041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75274</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>108650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228184</t>
+          <t>229394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>280676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>48131</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76991</t>
+          <t>77353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116917</t>
+          <t>116117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>38237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65992</t>
+          <t>66138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>100267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61630</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91224</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139273</t>
+          <t>137679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183745</t>
+          <t>180562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108415</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>146705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88437</t>
+          <t>88243</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179089</t>
+          <t>180365</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>226215</t>
+          <t>227921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55418</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>100900</t>
+          <t>102432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137855</t>
+          <t>139445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>43578</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69891</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152985</t>
+          <t>153176</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199852</t>
+          <t>198723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>32484</t>
+          <t>31044</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39913</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>91091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128013</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106722</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>140720</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207990</t>
+          <t>207659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257972</t>
+          <t>256714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>115572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154021</t>
+          <t>153031</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>59033</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88360</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182136</t>
+          <t>181321</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230231</t>
+          <t>229245</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>96707</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>83976</t>
+          <t>84968</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>119438</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>299810</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>366852</t>
+          <t>366867</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>127067</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>173185</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>441480</t>
+          <t>437395</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>525221</t>
+          <t>526131</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,49 +8360,49 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>20841</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>76748</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>117703</t>
+          <t>118006</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>340594</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>405357</t>
+          <t>408218</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>315662</t>
+          <t>315312</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>377319</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>678490</t>
+          <t>677740</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>768631</t>
+          <t>767122</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>494579</t>
+          <t>497830</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>571213</t>
+          <t>571310</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>270507</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>329850</t>
+          <t>327009</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>780944</t>
+          <t>777984</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>877448</t>
+          <t>874497</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50922</t>
+          <t>50967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40284</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>36079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>61596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47361</t>
+          <t>46687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74771</t>
+          <t>73975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>34547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88395</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>121563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>99978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129040</t>
+          <t>130627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55566</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79921</t>
+          <t>78989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162247</t>
+          <t>162666</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>200907</t>
+          <t>200811</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55071</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>48483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>96844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86652</t>
+          <t>84282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84669</t>
+          <t>86881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124030</t>
+          <t>125417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103271</t>
+          <t>101075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>142395</t>
+          <t>140476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68237</t>
+          <t>68851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>97922</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>177981</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>230462</t>
+          <t>227692</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125038</t>
+          <t>124535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165558</t>
+          <t>165631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62084</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90560</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198459</t>
+          <t>196012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246119</t>
+          <t>245625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>35389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95751</t>
+          <t>96663</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71074</t>
+          <t>69914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105803</t>
+          <t>103498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128005</t>
+          <t>128166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173349</t>
+          <t>170585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>39932</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>54908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64534</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97379</t>
+          <t>94851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53690</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81383</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126838</t>
+          <t>125992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168566</t>
+          <t>168214</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>108204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146034</t>
+          <t>146539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95221</t>
+          <t>95855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>182725</t>
+          <t>183589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230420</t>
+          <t>232334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>93349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>84372</t>
+          <t>83994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58270</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93797</t>
+          <t>94107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>136817</t>
+          <t>133924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27571</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>103109</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140201</t>
+          <t>140861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>120802</t>
+          <t>122785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156503</t>
+          <t>155215</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234116</t>
+          <t>235784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286706</t>
+          <t>288785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109656</t>
+          <t>111240</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147565</t>
+          <t>147644</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57380</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>86528</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>177130</t>
+          <t>178770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>223950</t>
+          <t>225028</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125564</t>
+          <t>124040</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>172246</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>100767</t>
+          <t>99210</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143257</t>
+          <t>141052</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>233643</t>
+          <t>237459</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>299563</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>222196</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>283537</t>
+          <t>281789</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>138871</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>184876</t>
+          <t>186838</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>377810</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>453865</t>
+          <t>452885</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>92895</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84491</t>
+          <t>85621</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>125812</t>
+          <t>127188</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>345134</t>
+          <t>346325</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>411814</t>
+          <t>415061</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>303707</t>
+          <t>302458</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>362837</t>
+          <t>364510</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>672496</t>
+          <t>665076</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>763169</t>
+          <t>759358</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>478631</t>
+          <t>478852</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>553039</t>
+          <t>551818</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>267843</t>
+          <t>268576</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>324600</t>
+          <t>326552</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>763154</t>
+          <t>764990</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>853926</t>
+          <t>856322</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
